--- a/data/50001589 - XEMORTIZ LA CANTERA III.xlsx
+++ b/data/50001589 - XEMORTIZ LA CANTERA III.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="317">
   <si>
     <t>50001589 - "XEMORTIZ LA CANTERA III"</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t xml:space="preserve">Generación OC corte laser  OT 4391 ,Fabricacion corte laser OT 4391 </t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1217603147834963</t>
@@ -2554,7 +2557,7 @@
       </c>
       <c r="C20" s="6"/>
       <c r="D20" s="5">
-        <v>46252.69687859954</v>
+        <v>46281.146999895835</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>78</v>
@@ -2598,8 +2601,8 @@
       <c r="R20" s="5">
         <v>46274</v>
       </c>
-      <c r="S20" s="7" t="s">
-        <v>33</v>
+      <c r="S20" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="T20" s="6">
         <v>0</v>
@@ -2610,7 +2613,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="9">
         <v>46252.556999583336</v>
@@ -2620,7 +2623,7 @@
         <v>46275.16982015046</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>26</v>
@@ -2653,7 +2656,7 @@
         <v>62</v>
       </c>
       <c r="P21" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
@@ -2669,7 +2672,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46252.5570037963</v>
@@ -2679,7 +2682,7 @@
         <v>46252.69698105324</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2709,10 +2712,10 @@
         <v>78</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Q22" s="6"/>
       <c r="R22" s="6"/>
@@ -2728,17 +2731,17 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B23" s="9">
         <v>46252.557008159725</v>
       </c>
       <c r="C23" s="10"/>
       <c r="D23" s="9">
-        <v>46252.69687457176</v>
+        <v>46281.14699958333</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>26</v>
@@ -2768,7 +2771,7 @@
         <v>77</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P23" s="10" t="s">
         <v>26</v>
@@ -2779,8 +2782,8 @@
       <c r="R23" s="9">
         <v>46274</v>
       </c>
-      <c r="S23" s="7" t="s">
-        <v>33</v>
+      <c r="S23" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="T23" s="10">
         <v>0</v>
@@ -2791,7 +2794,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46252.55701199074</v>
@@ -2828,13 +2831,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>68</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
@@ -2844,7 +2847,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="9">
         <v>46252.55701556713</v>
@@ -2854,7 +2857,7 @@
         <v>46252.69708273148</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>26</v>
@@ -2881,13 +2884,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O25" s="10" t="s">
         <v>69</v>
       </c>
       <c r="P25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="10"/>
@@ -2897,17 +2900,17 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="5">
         <v>46252.55701936343</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46252.696870659725</v>
+        <v>46281.1469994213</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -2937,7 +2940,7 @@
         <v>77</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -2948,8 +2951,8 @@
       <c r="R26" s="5">
         <v>46274</v>
       </c>
-      <c r="S26" s="7" t="s">
-        <v>33</v>
+      <c r="S26" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="T26" s="6">
         <v>0</v>
@@ -2960,7 +2963,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="9">
         <v>46252.55702353009</v>
@@ -2997,13 +3000,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O27" s="10" t="s">
         <v>74</v>
       </c>
       <c r="P27" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="10"/>
       <c r="R27" s="10"/>
@@ -3013,7 +3016,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" s="5">
         <v>46252.55702699074</v>
@@ -3023,7 +3026,7 @@
         <v>46252.697252893515</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3050,13 +3053,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>75</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3066,7 +3069,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" s="9">
         <v>46252.55703028935</v>
@@ -3076,16 +3079,16 @@
         <v>46252.697332800926</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I29" s="9">
         <v>46274</v>
@@ -3106,7 +3109,7 @@
         <v>77</v>
       </c>
       <c r="O29" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P29" s="10" t="s">
         <v>26</v>
@@ -3129,7 +3132,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5">
         <v>46252.55703413194</v>
@@ -3139,16 +3142,16 @@
         <v>46255.628655023145</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I30" s="5">
         <v>46274</v>
@@ -3166,13 +3169,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3182,7 +3185,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" s="9">
         <v>46252.55703804398</v>
@@ -3192,16 +3195,16 @@
         <v>46252.697425763894</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I31" s="9">
         <v>46286</v>
@@ -3219,13 +3222,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P31" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
@@ -3235,7 +3238,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46252.55704118055</v>
@@ -3245,16 +3248,16 @@
         <v>46252.69750998843</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I32" s="5">
         <v>46315</v>
@@ -3272,13 +3275,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3288,7 +3291,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="9">
         <v>46252.557044560184</v>
@@ -3298,7 +3301,7 @@
         <v>46252.97582111111</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>25</v>
@@ -3322,7 +3325,7 @@
         <v>26</v>
       </c>
       <c r="O33" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="10" t="s">
         <v>26</v>
@@ -3335,7 +3338,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46252.55704748843</v>
@@ -3347,16 +3350,16 @@
         <v>46262.175324780095</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46255</v>
@@ -3374,13 +3377,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="5">
         <v>46261</v>
@@ -3400,7 +3403,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="9">
         <v>46252.557051701384</v>
@@ -3412,16 +3415,16 @@
         <v>46269.18259631944</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I35" s="9">
         <v>46262</v>
@@ -3439,13 +3442,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O35" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P35" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="9">
         <v>46268</v>
@@ -3465,7 +3468,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46252.557056122685</v>
@@ -3481,10 +3484,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I36" s="5">
         <v>46269</v>
@@ -3502,13 +3505,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="Q36" s="5">
         <v>46269</v>
@@ -3528,7 +3531,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="9">
         <v>46252.55706707176</v>
@@ -3538,16 +3541,16 @@
         <v>46252.69802949074</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I37" s="9">
         <v>46317</v>
@@ -3565,13 +3568,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O37" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P37" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q37" s="9">
         <v>46317</v>
@@ -3591,7 +3594,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B38" s="5">
         <v>46252.55707230324</v>
@@ -3601,16 +3604,16 @@
         <v>46252.69812450232</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I38" s="5">
         <v>46317</v>
@@ -3628,13 +3631,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3644,7 +3647,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="9">
         <v>46252.55710016204</v>
@@ -3654,16 +3657,16 @@
         <v>46252.69812077546</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I39" s="9">
         <v>46317</v>
@@ -3681,13 +3684,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O39" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -3697,7 +3700,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46252.55707606481</v>
@@ -3707,16 +3710,16 @@
         <v>46252.69811745371</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I40" s="5">
         <v>46317</v>
@@ -3734,13 +3737,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -3750,7 +3753,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" s="9">
         <v>46252.557103796295</v>
@@ -3760,16 +3763,16 @@
         <v>46252.69811380787</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I41" s="9">
         <v>46317</v>
@@ -3787,13 +3790,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O41" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P41" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -3803,7 +3806,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46252.5571797338</v>
@@ -3813,7 +3816,7 @@
         <v>46252.68940578704</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>25</v>
@@ -3837,7 +3840,7 @@
         <v>26</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>26</v>
@@ -3850,7 +3853,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="9">
         <v>46252.5571834375</v>
@@ -3860,16 +3863,16 @@
         <v>46252.69824100695</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" s="9">
         <v>46289</v>
@@ -3887,13 +3890,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P43" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="Q43" s="9">
         <v>46289</v>
@@ -3913,7 +3916,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46252.55718878472</v>
@@ -3923,16 +3926,16 @@
         <v>46252.69823666666</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46289</v>
@@ -3950,13 +3953,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="5">
         <v>46289</v>
@@ -3976,7 +3979,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="9">
         <v>46252.55719385417</v>
@@ -3986,16 +3989,16 @@
         <v>46252.69823263889</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" s="9">
         <v>46289</v>
@@ -4013,13 +4016,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O45" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P45" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="9">
         <v>46289</v>
@@ -4039,7 +4042,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46252.55719849537</v>
@@ -4049,16 +4052,16 @@
         <v>46252.69832325232</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I46" s="5">
         <v>46290</v>
@@ -4076,13 +4079,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q46" s="5">
         <v>46290</v>
@@ -4102,7 +4105,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B47" s="9">
         <v>46252.55720311342</v>
@@ -4112,16 +4115,16 @@
         <v>46252.69831820602</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I47" s="9">
         <v>46290</v>
@@ -4139,13 +4142,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O47" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P47" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="9">
         <v>46290</v>
@@ -4165,7 +4168,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46252.55720751158</v>
@@ -4175,16 +4178,16 @@
         <v>46252.69831280093</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I48" s="5">
         <v>46290</v>
@@ -4202,13 +4205,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="5">
         <v>46290</v>
@@ -4228,7 +4231,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B49" s="9">
         <v>46252.557211990745</v>
@@ -4238,7 +4241,7 @@
         <v>46252.69068731481</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>25</v>
@@ -4262,7 +4265,7 @@
         <v>26</v>
       </c>
       <c r="O49" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="P49" s="10" t="s">
         <v>26</v>
@@ -4275,7 +4278,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46252.55721460648</v>
@@ -4285,16 +4288,16 @@
         <v>46252.70057114583</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I50" s="5">
         <v>46293</v>
@@ -4312,13 +4315,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>71</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q50" s="5">
         <v>46295</v>
@@ -4338,7 +4341,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" s="9">
         <v>46252.55722055555</v>
@@ -4348,16 +4351,16 @@
         <v>46252.70066232639</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I51" s="9">
         <v>46296</v>
@@ -4375,13 +4378,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O51" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P51" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q51" s="9">
         <v>46302</v>
@@ -4401,7 +4404,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46252.55722498843</v>
@@ -4411,16 +4414,16 @@
         <v>46252.69860596065</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I52" s="5">
         <v>46296</v>
@@ -4438,13 +4441,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4454,7 +4457,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B53" s="9">
         <v>46252.557231053244</v>
@@ -4464,16 +4467,16 @@
         <v>46252.698601689815</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I53" s="9">
         <v>46296</v>
@@ -4491,13 +4494,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O53" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P53" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q53" s="10"/>
       <c r="R53" s="10"/>
@@ -4507,7 +4510,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46252.55723662037</v>
@@ -4517,16 +4520,16 @@
         <v>46252.69859731481</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I54" s="5">
         <v>46296</v>
@@ -4544,13 +4547,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -4560,7 +4563,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B55" s="9">
         <v>46252.55724217593</v>
@@ -4570,16 +4573,16 @@
         <v>46252.698592395835</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I55" s="9">
         <v>46296</v>
@@ -4597,13 +4600,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O55" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P55" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q55" s="10"/>
       <c r="R55" s="10"/>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B56" s="5">
         <v>46252.55725293982</v>
@@ -4623,16 +4626,16 @@
         <v>46252.70073358796</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I56" s="5">
         <v>46303</v>
@@ -4650,13 +4653,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q56" s="5">
         <v>46303</v>
@@ -4676,7 +4679,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B57" s="9">
         <v>46252.55725741899</v>
@@ -4686,16 +4689,16 @@
         <v>46252.698911064814</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I57" s="9">
         <v>46303</v>
@@ -4713,13 +4716,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O57" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P57" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q57" s="10"/>
       <c r="R57" s="10"/>
@@ -4729,7 +4732,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B58" s="5">
         <v>46252.557269537036</v>
@@ -4739,16 +4742,16 @@
         <v>46252.69921875</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I58" s="5">
         <v>46303</v>
@@ -4766,13 +4769,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -4782,7 +4785,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B59" s="9">
         <v>46252.55727405092</v>
@@ -4792,16 +4795,16 @@
         <v>46252.699140439814</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I59" s="9">
         <v>46303</v>
@@ -4819,13 +4822,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O59" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="P59" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q59" s="10"/>
       <c r="R59" s="10"/>
@@ -4835,7 +4838,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B60" s="5">
         <v>46252.55727831018</v>
@@ -4845,16 +4848,16 @@
         <v>46252.69907054398</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I60" s="5">
         <v>46303</v>
@@ -4872,13 +4875,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -4888,7 +4891,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B61" s="9">
         <v>46252.55728853009</v>
@@ -4898,7 +4901,7 @@
         <v>46252.6910509375</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>25</v>
@@ -4922,7 +4925,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P61" s="10" t="s">
         <v>26</v>
@@ -4935,7 +4938,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B62" s="5">
         <v>46252.5572910301</v>
@@ -4945,16 +4948,16 @@
         <v>46259.18503317129</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I62" s="5">
         <v>46258</v>
@@ -4972,13 +4975,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>49</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q62" s="5">
         <v>46258</v>
@@ -4998,7 +5001,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="9">
         <v>46252.55729690973</v>
@@ -5008,16 +5011,16 @@
         <v>46259.185033726855</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I63" s="9">
         <v>46258</v>
@@ -5035,13 +5038,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O63" s="10" t="s">
         <v>55</v>
       </c>
       <c r="P63" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q63" s="9">
         <v>46258</v>
@@ -5061,7 +5064,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B64" s="5">
         <v>46252.557346898146</v>
@@ -5071,16 +5074,16 @@
         <v>46259.18503320602</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I64" s="5">
         <v>46258</v>
@@ -5098,13 +5101,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q64" s="5">
         <v>46258</v>
@@ -5124,7 +5127,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B65" s="9">
         <v>46252.55735335648</v>
@@ -5134,7 +5137,7 @@
         <v>46252.702101076386</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>25</v>
@@ -5158,7 +5161,7 @@
         <v>26</v>
       </c>
       <c r="O65" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P65" s="10" t="s">
         <v>26</v>
@@ -5171,7 +5174,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B66" s="5">
         <v>46252.55735695602</v>
@@ -5181,7 +5184,7 @@
         <v>46252.7008559838</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5208,13 +5211,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q66" s="5">
         <v>46310</v>
@@ -5234,7 +5237,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B67" s="9">
         <v>46252.55736157407</v>
@@ -5244,7 +5247,7 @@
         <v>46252.69178234954</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>26</v>
@@ -5269,13 +5272,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O67" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P67" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="10"/>
       <c r="R67" s="10"/>
@@ -5285,7 +5288,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B68" s="5">
         <v>46252.55736651621</v>
@@ -5295,7 +5298,7 @@
         <v>46252.69178262731</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
@@ -5320,13 +5323,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -5336,7 +5339,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B69" s="9">
         <v>46252.5573705787</v>
@@ -5346,7 +5349,7 @@
         <v>46252.69178273148</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>26</v>
@@ -5371,13 +5374,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O69" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P69" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q69" s="10"/>
       <c r="R69" s="10"/>
@@ -5387,7 +5390,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B70" s="5">
         <v>46252.557374861106</v>
@@ -5397,7 +5400,7 @@
         <v>46252.69178283565</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
@@ -5422,13 +5425,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5438,7 +5441,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B71" s="9">
         <v>46252.557386238426</v>
@@ -5448,7 +5451,7 @@
         <v>46252.7009634375</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F71" s="10" t="s">
         <v>26</v>
@@ -5473,13 +5476,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O71" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P71" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q71" s="9">
         <v>46311</v>
@@ -5499,7 +5502,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B72" s="5">
         <v>46252.557390752314</v>
@@ -5509,7 +5512,7 @@
         <v>46252.701506087964</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -5536,13 +5539,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5552,7 +5555,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B73" s="9">
         <v>46252.55739621528</v>
@@ -5562,7 +5565,7 @@
         <v>46252.70150201389</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F73" s="10" t="s">
         <v>26</v>
@@ -5589,13 +5592,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O73" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P73" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q73" s="10"/>
       <c r="R73" s="10"/>
@@ -5605,7 +5608,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B74" s="5">
         <v>46252.55740107639</v>
@@ -5615,7 +5618,7 @@
         <v>46252.70149827546</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -5642,13 +5645,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -5658,7 +5661,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B75" s="9">
         <v>46252.55740615741</v>
@@ -5668,7 +5671,7 @@
         <v>46252.701494340276</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F75" s="10" t="s">
         <v>26</v>
@@ -5695,13 +5698,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O75" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P75" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q75" s="10"/>
       <c r="R75" s="10"/>
@@ -5711,7 +5714,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B76" s="5">
         <v>46252.55741842593</v>
@@ -5721,7 +5724,7 @@
         <v>46252.701071006944</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5748,13 +5751,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q76" s="5">
         <v>46314</v>
@@ -5774,7 +5777,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B77" s="9">
         <v>46252.55743083333</v>
@@ -5784,7 +5787,7 @@
         <v>46252.701612997684</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F77" s="10" t="s">
         <v>26</v>
@@ -5811,13 +5814,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O77" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P77" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q77" s="10"/>
       <c r="R77" s="10"/>
@@ -5827,7 +5830,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B78" s="5">
         <v>46252.55743526621</v>
@@ -5837,7 +5840,7 @@
         <v>46252.70160922453</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
@@ -5864,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -5880,7 +5883,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B79" s="9">
         <v>46252.55743940972</v>
@@ -5890,7 +5893,7 @@
         <v>46252.70160523149</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>26</v>
@@ -5917,13 +5920,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O79" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P79" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q79" s="10"/>
       <c r="R79" s="10"/>
@@ -5933,7 +5936,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B80" s="5">
         <v>46252.557443564816</v>
@@ -5943,7 +5946,7 @@
         <v>46252.70160128472</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
@@ -5970,13 +5973,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -5986,7 +5989,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B81" s="9">
         <v>46252.55745417824</v>
@@ -5996,7 +5999,7 @@
         <v>46252.70116899305</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>26</v>
@@ -6023,13 +6026,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O81" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P81" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q81" s="9">
         <v>46315</v>
@@ -6049,7 +6052,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B82" s="5">
         <v>46252.55745881944</v>
@@ -6059,7 +6062,7 @@
         <v>46252.70171259259</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
@@ -6086,13 +6089,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6102,7 +6105,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B83" s="9">
         <v>46252.55746319445</v>
@@ -6112,7 +6115,7 @@
         <v>46252.7017084375</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>26</v>
@@ -6139,13 +6142,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O83" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P83" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q83" s="10"/>
       <c r="R83" s="10"/>
@@ -6155,7 +6158,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B84" s="5">
         <v>46252.55746769676</v>
@@ -6165,7 +6168,7 @@
         <v>46252.701704120365</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6192,13 +6195,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
@@ -6208,7 +6211,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B85" s="9">
         <v>46252.557471886576</v>
@@ -6218,7 +6221,7 @@
         <v>46252.70169959491</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>26</v>
@@ -6245,13 +6248,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O85" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P85" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q85" s="10"/>
       <c r="R85" s="10"/>
@@ -6261,7 +6264,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B86" s="5">
         <v>46252.55752560185</v>
@@ -6271,7 +6274,7 @@
         <v>46252.70126476852</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6298,13 +6301,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q86" s="5">
         <v>46316</v>
@@ -6324,7 +6327,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B87" s="9">
         <v>46252.5575312037</v>
@@ -6334,7 +6337,7 @@
         <v>46252.70181533565</v>
       </c>
       <c r="E87" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>26</v>
@@ -6361,13 +6364,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O87" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P87" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q87" s="10"/>
       <c r="R87" s="10"/>
@@ -6377,7 +6380,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B88" s="5">
         <v>46252.55753719907</v>
@@ -6387,7 +6390,7 @@
         <v>46252.70181135417</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6414,13 +6417,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6430,7 +6433,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B89" s="9">
         <v>46252.55754401621</v>
@@ -6440,7 +6443,7 @@
         <v>46252.701807418984</v>
       </c>
       <c r="E89" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>26</v>
@@ -6467,13 +6470,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O89" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P89" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q89" s="10"/>
       <c r="R89" s="10"/>
@@ -6483,7 +6486,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B90" s="5">
         <v>46252.55754952546</v>
@@ -6493,7 +6496,7 @@
         <v>46252.701803240736</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -6520,13 +6523,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -6536,7 +6539,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B91" s="9">
         <v>46252.55756099537</v>
@@ -6546,7 +6549,7 @@
         <v>46252.702279386576</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F91" s="10" t="s">
         <v>26</v>
@@ -6573,13 +6576,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O91" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P91" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q91" s="9">
         <v>46318</v>
@@ -6599,7 +6602,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B92" s="5">
         <v>46252.5575653125</v>
@@ -6609,7 +6612,7 @@
         <v>46252.702298738426</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -6636,13 +6639,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -6652,7 +6655,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B93" s="9">
         <v>46252.55756915509</v>
@@ -6662,7 +6665,7 @@
         <v>46252.702299490746</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F93" s="10" t="s">
         <v>26</v>
@@ -6689,13 +6692,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O93" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P93" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q93" s="10"/>
       <c r="R93" s="10"/>
@@ -6705,7 +6708,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B94" s="5">
         <v>46252.557572731486</v>
@@ -6715,7 +6718,7 @@
         <v>46252.70230001157</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -6742,13 +6745,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -6758,7 +6761,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B95" s="9">
         <v>46252.557576770836</v>
@@ -6768,7 +6771,7 @@
         <v>46252.70230050926</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F95" s="10" t="s">
         <v>26</v>
@@ -6795,13 +6798,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O95" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P95" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q95" s="10"/>
       <c r="R95" s="10"/>
@@ -6811,7 +6814,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B96" s="5">
         <v>46252.557587118055</v>
@@ -6821,7 +6824,7 @@
         <v>46252.70255065973</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -6845,7 +6848,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -6858,7 +6861,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B97" s="9">
         <v>46252.55759005787</v>
@@ -6868,16 +6871,16 @@
         <v>46252.703546226854</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F97" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H97" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I97" s="9">
         <v>46321</v>
@@ -6895,13 +6898,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O97" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P97" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q97" s="9">
         <v>46321</v>
@@ -6921,7 +6924,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B98" s="5">
         <v>46252.55759454861</v>
@@ -6931,16 +6934,16 @@
         <v>46252.70282324074</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I98" s="5">
         <v>46321</v>
@@ -6958,13 +6961,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -6974,7 +6977,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B99" s="9">
         <v>46252.557597962965</v>
@@ -6984,16 +6987,16 @@
         <v>46252.702824618056</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F99" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H99" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I99" s="9">
         <v>46321</v>
@@ -7011,13 +7014,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O99" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P99" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q99" s="10"/>
       <c r="R99" s="10"/>
@@ -7027,7 +7030,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B100" s="5">
         <v>46252.55760144676</v>
@@ -7037,16 +7040,16 @@
         <v>46252.702825775465</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I100" s="5">
         <v>46321</v>
@@ -7064,13 +7067,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7080,7 +7083,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B101" s="9">
         <v>46252.55760519676</v>
@@ -7090,16 +7093,16 @@
         <v>46252.702826354165</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F101" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H101" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I101" s="9">
         <v>46321</v>
@@ -7117,13 +7120,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="O101" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P101" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q101" s="10"/>
       <c r="R101" s="10"/>
@@ -7133,7 +7136,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B102" s="5">
         <v>46252.55761483796</v>
@@ -7143,7 +7146,7 @@
         <v>46252.703109884256</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7170,10 +7173,10 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7196,7 +7199,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B103" s="9">
         <v>46252.55761875</v>
@@ -7206,7 +7209,7 @@
         <v>46252.70303388889</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F103" s="10" t="s">
         <v>26</v>
@@ -7233,13 +7236,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O103" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P103" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q103" s="10"/>
       <c r="R103" s="10"/>
@@ -7249,7 +7252,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B104" s="5">
         <v>46252.55762228009</v>
@@ -7259,7 +7262,7 @@
         <v>46252.70302983796</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7286,13 +7289,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7302,7 +7305,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B105" s="9">
         <v>46252.557631655094</v>
@@ -7312,7 +7315,7 @@
         <v>46252.70302586806</v>
       </c>
       <c r="E105" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>26</v>
@@ -7339,13 +7342,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O105" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P105" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q105" s="10"/>
       <c r="R105" s="10"/>
@@ -7355,7 +7358,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B106" s="5">
         <v>46252.557635370365</v>
@@ -7365,7 +7368,7 @@
         <v>46252.703022002315</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7392,13 +7395,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7408,7 +7411,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B107" s="9">
         <v>46252.557645277775</v>
@@ -7418,16 +7421,16 @@
         <v>46252.7034387037</v>
       </c>
       <c r="E107" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F107" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H107" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I107" s="9">
         <v>46322</v>
@@ -7445,13 +7448,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O107" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P107" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q107" s="9">
         <v>46322</v>
@@ -7471,7 +7474,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B108" s="5">
         <v>46252.55764945602</v>
@@ -7481,16 +7484,16 @@
         <v>46252.703307407406</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I108" s="5">
         <v>46323</v>
@@ -7508,13 +7511,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -7524,7 +7527,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B109" s="9">
         <v>46252.55765310185</v>
@@ -7534,16 +7537,16 @@
         <v>46252.703303483795</v>
       </c>
       <c r="E109" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F109" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I109" s="9">
         <v>46323</v>
@@ -7561,13 +7564,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O109" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P109" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q109" s="10"/>
       <c r="R109" s="10"/>
@@ -7577,7 +7580,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B110" s="5">
         <v>46252.557656550925</v>
@@ -7587,16 +7590,16 @@
         <v>46252.70329978009</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I110" s="5">
         <v>46323</v>
@@ -7614,13 +7617,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -7630,7 +7633,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B111" s="9">
         <v>46252.55766010417</v>
@@ -7640,16 +7643,16 @@
         <v>46252.70329600695</v>
       </c>
       <c r="E111" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H111" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I111" s="9">
         <v>46323</v>
@@ -7667,13 +7670,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O111" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P111" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q111" s="10"/>
       <c r="R111" s="10"/>
@@ -7683,7 +7686,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B112" s="5">
         <v>46252.55771944445</v>
@@ -7693,16 +7696,16 @@
         <v>46252.704073796296</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I112" s="5">
         <v>46323</v>
@@ -7720,13 +7723,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q112" s="5">
         <v>46323</v>
@@ -7746,7 +7749,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="8" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B113" s="9">
         <v>46252.55772550926</v>
@@ -7756,16 +7759,16 @@
         <v>46252.70394047454</v>
       </c>
       <c r="E113" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H113" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I113" s="9">
         <v>46323</v>
@@ -7783,13 +7786,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O113" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P113" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q113" s="10"/>
       <c r="R113" s="10"/>
@@ -7799,7 +7802,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B114" s="5">
         <v>46252.557729016204</v>
@@ -7809,16 +7812,16 @@
         <v>46252.70393585648</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I114" s="5">
         <v>46323</v>
@@ -7836,13 +7839,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -7852,7 +7855,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B115" s="9">
         <v>46252.55773266204</v>
@@ -7862,16 +7865,16 @@
         <v>46252.70393150463</v>
       </c>
       <c r="E115" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F115" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I115" s="9">
         <v>46323</v>
@@ -7889,13 +7892,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O115" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P115" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q115" s="10"/>
       <c r="R115" s="10"/>
@@ -7905,7 +7908,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B116" s="5">
         <v>46252.557736111106</v>
@@ -7915,16 +7918,16 @@
         <v>46252.703926898146</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I116" s="5">
         <v>46323</v>
@@ -7942,13 +7945,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -7958,7 +7961,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B117" s="9">
         <v>46252.55774533565</v>
@@ -7968,7 +7971,7 @@
         <v>46252.695085370375</v>
       </c>
       <c r="E117" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>25</v>
@@ -7992,7 +7995,7 @@
         <v>26</v>
       </c>
       <c r="O117" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P117" s="10" t="s">
         <v>26</v>
@@ -8005,7 +8008,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B118" s="5">
         <v>46252.557748136576</v>
@@ -8015,16 +8018,16 @@
         <v>46252.70404589121</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I118" s="5">
         <v>46324</v>
@@ -8042,13 +8045,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q118" s="5">
         <v>46332</v>
@@ -8068,7 +8071,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B119" s="9">
         <v>46252.55775356482</v>
@@ -8078,16 +8081,16 @@
         <v>46252.704042094905</v>
       </c>
       <c r="E119" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F119" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I119" s="9">
         <v>46324</v>
@@ -8105,13 +8108,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O119" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P119" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q119" s="9">
         <v>46332</v>

--- a/data/50001589 - XEMORTIZ LA CANTERA III.xlsx
+++ b/data/50001589 - XEMORTIZ LA CANTERA III.xlsx
@@ -3139,7 +3139,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46255.628655023145</v>
+        <v>46282.169089814815</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="C43" s="10"/>
       <c r="D43" s="9">
-        <v>46252.69824100695</v>
+        <v>46282.16401299769</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>153</v>
@@ -3904,8 +3904,8 @@
       <c r="R43" s="9">
         <v>46289</v>
       </c>
-      <c r="S43" s="7" t="s">
-        <v>33</v>
+      <c r="S43" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="T43" s="10">
         <v>0</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46252.69823666666</v>
+        <v>46282.164015208335</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>158</v>
@@ -3967,8 +3967,8 @@
       <c r="R44" s="5">
         <v>46289</v>
       </c>
-      <c r="S44" s="7" t="s">
-        <v>33</v>
+      <c r="S44" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="C45" s="10"/>
       <c r="D45" s="9">
-        <v>46252.69823263889</v>
+        <v>46282.164013113426</v>
       </c>
       <c r="E45" s="10" t="s">
         <v>161</v>
@@ -4030,8 +4030,8 @@
       <c r="R45" s="9">
         <v>46289</v>
       </c>
-      <c r="S45" s="7" t="s">
-        <v>33</v>
+      <c r="S45" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="T45" s="10">
         <v>0</v>
